--- a/output/quickfixopen2_all_markets_daily.xlsx
+++ b/output/quickfixopen2_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixopen2 daily (exit = the open of price bar 2), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-30); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-31 15:45 UTC.</t>
+          <t>quickfixopen2 daily (exit = the open of price bar 2), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-30); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-31 17:02 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixopen2_all_markets_daily.xlsx
+++ b/output/quickfixopen2_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F5" t="n">
         <v>8</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -927,7 +927,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -938,17 +938,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -963,19 +963,19 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5.75</v>
+        <v>6.95</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>105745.47</v>
+        <v>106953.26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -986,17 +986,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -1008,16 +1008,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4.61</v>
+        <v>5.75</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>104610</v>
+        <v>105745.47</v>
       </c>
     </row>
     <row r="12">
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1178,11 +1178,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -1226,11 +1226,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1271,11 +1271,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1316,11 +1316,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1361,11 +1361,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1406,11 +1406,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1451,11 +1451,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F22" t="n">
         <v>2</v>
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixopen2 daily (exit = the open of price bar 2), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-30); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-31 17:02 UTC.</t>
+          <t>quickfixopen2 daily (exit = the open of price bar 2), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 19:43 UTC.</t>
         </is>
       </c>
     </row>
@@ -5536,22 +5536,39 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>2</v>
+      </c>
       <c r="G55" t="n">
         <v>2.69</v>
       </c>
       <c r="H55" t="n">
         <v>2.665</v>
       </c>
+      <c r="J55" t="n">
+        <v>2.746</v>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>2.24</v>
       </c>
       <c r="N55" t="n">
         <v>104610</v>
       </c>
       <c r="O55" t="n">
-        <v>104610</v>
+        <v>106953.26</v>
       </c>
     </row>
     <row r="56">

--- a/output/quickfixopen2_all_markets_daily.xlsx
+++ b/output/quickfixopen2_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixopen2 daily (exit = the open of price bar 2), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 19:43 UTC.</t>
+          <t>quickfixopen2 daily (exit = the open of price bar 2), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 22:59 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixopen2_all_markets_daily.xlsx
+++ b/output/quickfixopen2_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixopen2 daily (exit = the open of price bar 2), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 22:59 UTC.</t>
+          <t>quickfixopen2 daily (exit = the open of price bar 2), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-02 00:09 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixopen2_all_markets_daily.xlsx
+++ b/output/quickfixopen2_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F5" t="n">
         <v>8</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1178,11 +1178,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -1226,11 +1226,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1271,11 +1271,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1316,11 +1316,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1361,11 +1361,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1406,11 +1406,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1451,11 +1451,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F22" t="n">
         <v>2</v>
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixopen2 daily (exit = the open of price bar 2), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-02 00:09 UTC.</t>
+          <t>quickfixopen2 daily (exit = the open of price bar 2), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-04); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-05 13:32 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixopen2_all_markets_daily.xlsx
+++ b/output/quickfixopen2_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F5" t="n">
         <v>8</v>
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>75</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>75</v>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1056,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>100</v>
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1178,11 +1178,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -1226,11 +1226,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1271,11 +1271,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1316,11 +1316,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1361,11 +1361,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1406,11 +1406,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1451,11 +1451,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F22" t="n">
         <v>2</v>
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixopen2 daily (exit = the open of price bar 2), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-04); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-05 13:32 UTC.</t>
+          <t>quickfixopen2 daily (exit = the open of price bar 2), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-06); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-07 13:34 UTC.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O89"/>
+  <dimension ref="A1:O93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4926,11 +4926,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4939,48 +4939,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>2</v>
+          <t>2026-08-06</t>
+        </is>
       </c>
       <c r="G44" t="n">
-        <v>0.006417</v>
+        <v>4305.3</v>
       </c>
       <c r="H44" t="n">
-        <v>0.006454</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.006386</v>
+        <v>4363.8</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>exit_open</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>0.8243</v>
-      </c>
-      <c r="M44" s="2" t="n">
-        <v>0.8243</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N44" t="n">
-        <v>100000</v>
+        <v>117885.42</v>
       </c>
       <c r="O44" t="n">
-        <v>100824.32</v>
+        <v>117885.42</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Japanese_Yen_Futures</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -4993,42 +4976,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" t="n">
-        <v>239.06</v>
+        <v>0.006417</v>
       </c>
       <c r="H45" t="n">
-        <v>239.73</v>
+        <v>0.006454</v>
       </c>
       <c r="J45" t="n">
-        <v>239.73</v>
+        <v>0.006386</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_open</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M45" s="5" t="n">
-        <v>-1</v>
+        <v>0.8243</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>0.8243</v>
       </c>
       <c r="N45" t="n">
         <v>100000</v>
       </c>
       <c r="O45" t="n">
-        <v>99000</v>
+        <v>100824.32</v>
       </c>
     </row>
     <row r="46">
@@ -5038,7 +5021,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5047,42 +5030,42 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>251.58</v>
+        <v>239.06</v>
       </c>
       <c r="H46" t="n">
-        <v>251.91</v>
+        <v>239.73</v>
       </c>
       <c r="J46" t="n">
-        <v>247.67</v>
+        <v>239.73</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>11.8485</v>
-      </c>
-      <c r="M46" s="2" t="n">
-        <v>11.8485</v>
+        <v>-1</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N46" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O46" t="n">
         <v>99000</v>
-      </c>
-      <c r="O46" t="n">
-        <v>110730</v>
       </c>
     </row>
     <row r="47">
@@ -5092,7 +5075,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5101,25 +5084,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>2</v>
       </c>
       <c r="G47" t="n">
-        <v>255.38</v>
+        <v>251.58</v>
       </c>
       <c r="H47" t="n">
-        <v>256.63</v>
+        <v>251.91</v>
       </c>
       <c r="J47" t="n">
-        <v>253</v>
+        <v>247.67</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -5127,16 +5110,16 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.904</v>
+        <v>11.8485</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1.904</v>
+        <v>11.8485</v>
       </c>
       <c r="N47" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O47" t="n">
         <v>110730</v>
-      </c>
-      <c r="O47" t="n">
-        <v>112838.3</v>
       </c>
     </row>
     <row r="48">
@@ -5146,34 +5129,34 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>2</v>
       </c>
       <c r="G48" t="n">
-        <v>235.2</v>
+        <v>255.38</v>
       </c>
       <c r="H48" t="n">
-        <v>234.36</v>
+        <v>256.63</v>
       </c>
       <c r="J48" t="n">
-        <v>235.5</v>
+        <v>253</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -5181,26 +5164,26 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0.3571</v>
+        <v>1.904</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.3571</v>
+        <v>1.904</v>
       </c>
       <c r="N48" t="n">
+        <v>110730</v>
+      </c>
+      <c r="O48" t="n">
         <v>112838.3</v>
-      </c>
-      <c r="O48" t="n">
-        <v>113241.29</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5209,42 +5192,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
-        <v>5.7714</v>
+        <v>235.2</v>
       </c>
       <c r="H49" t="n">
-        <v>5.6849</v>
+        <v>234.36</v>
       </c>
       <c r="J49" t="n">
-        <v>5.6849</v>
+        <v>235.5</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_open</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M49" s="5" t="n">
-        <v>-1</v>
+        <v>0.3571</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>0.3571</v>
       </c>
       <c r="N49" t="n">
-        <v>100000</v>
+        <v>112838.3</v>
       </c>
       <c r="O49" t="n">
-        <v>99000</v>
+        <v>113241.29</v>
       </c>
     </row>
     <row r="50">
@@ -5254,7 +5237,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5263,12 +5246,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -5278,10 +5261,10 @@
         <v>5.7714</v>
       </c>
       <c r="H50" t="n">
-        <v>5.6774</v>
+        <v>5.6849</v>
       </c>
       <c r="J50" t="n">
-        <v>5.6774</v>
+        <v>5.6849</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -5295,10 +5278,10 @@
         <v>-1</v>
       </c>
       <c r="N50" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O50" t="n">
         <v>99000</v>
-      </c>
-      <c r="O50" t="n">
-        <v>98010</v>
       </c>
     </row>
     <row r="51">
@@ -5308,7 +5291,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5317,42 +5300,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>5.3133</v>
+        <v>5.7714</v>
       </c>
       <c r="H51" t="n">
-        <v>5.2459</v>
+        <v>5.6774</v>
       </c>
       <c r="J51" t="n">
-        <v>5.5585</v>
+        <v>5.6774</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.638</v>
-      </c>
-      <c r="M51" s="2" t="n">
-        <v>3.638</v>
+        <v>-1</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N51" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O51" t="n">
         <v>98010</v>
-      </c>
-      <c r="O51" t="n">
-        <v>101575.59</v>
       </c>
     </row>
     <row r="52">
@@ -5362,34 +5345,34 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>2</v>
       </c>
       <c r="G52" t="n">
-        <v>6.0956</v>
+        <v>5.3133</v>
       </c>
       <c r="H52" t="n">
-        <v>6.1481</v>
+        <v>5.2459</v>
       </c>
       <c r="J52" t="n">
-        <v>6.037</v>
+        <v>5.5585</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -5397,26 +5380,26 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.1162</v>
+        <v>3.638</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1.1162</v>
+        <v>3.638</v>
       </c>
       <c r="N52" t="n">
+        <v>98010</v>
+      </c>
+      <c r="O52" t="n">
         <v>101575.59</v>
-      </c>
-      <c r="O52" t="n">
-        <v>102709.36</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5425,42 +5408,42 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>3.305</v>
+        <v>6.0956</v>
       </c>
       <c r="H53" t="n">
-        <v>3.354</v>
+        <v>6.1481</v>
       </c>
       <c r="J53" t="n">
-        <v>3.354</v>
+        <v>6.037</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_open</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M53" s="5" t="n">
-        <v>-1</v>
+        <v>1.1162</v>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>1.1162</v>
       </c>
       <c r="N53" t="n">
-        <v>100000</v>
+        <v>101575.59</v>
       </c>
       <c r="O53" t="n">
-        <v>99000</v>
+        <v>102709.36</v>
       </c>
     </row>
     <row r="54">
@@ -5470,7 +5453,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -5479,42 +5462,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
         <v>3.305</v>
       </c>
       <c r="H54" t="n">
-        <v>3.356</v>
+        <v>3.354</v>
       </c>
       <c r="J54" t="n">
-        <v>3.016</v>
+        <v>3.354</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>5.6667</v>
-      </c>
-      <c r="M54" s="2" t="n">
-        <v>5.6667</v>
+        <v>-1</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N54" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O54" t="n">
         <v>99000</v>
-      </c>
-      <c r="O54" t="n">
-        <v>104610</v>
       </c>
     </row>
     <row r="55">
@@ -5524,34 +5507,34 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>2</v>
       </c>
       <c r="G55" t="n">
-        <v>2.69</v>
+        <v>3.305</v>
       </c>
       <c r="H55" t="n">
-        <v>2.665</v>
+        <v>3.356</v>
       </c>
       <c r="J55" t="n">
-        <v>2.746</v>
+        <v>3.016</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -5559,26 +5542,26 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.24</v>
+        <v>5.6667</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2.24</v>
+        <v>5.6667</v>
       </c>
       <c r="N55" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O55" t="n">
         <v>104610</v>
-      </c>
-      <c r="O55" t="n">
-        <v>106953.26</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -5587,25 +5570,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>1360.4</v>
+        <v>2.69</v>
       </c>
       <c r="H56" t="n">
-        <v>1343.4</v>
+        <v>2.665</v>
       </c>
       <c r="J56" t="n">
-        <v>1364.5</v>
+        <v>2.746</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -5613,16 +5596,16 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0.2412</v>
+        <v>2.24</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.2412</v>
+        <v>2.24</v>
       </c>
       <c r="N56" t="n">
-        <v>100000</v>
+        <v>104610</v>
       </c>
       <c r="O56" t="n">
-        <v>100241.18</v>
+        <v>106953.26</v>
       </c>
     </row>
     <row r="57">
@@ -5632,7 +5615,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -5641,25 +5624,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>2</v>
       </c>
       <c r="G57" t="n">
-        <v>1167</v>
+        <v>1360.4</v>
       </c>
       <c r="H57" t="n">
-        <v>1159.4</v>
+        <v>1343.4</v>
       </c>
       <c r="J57" t="n">
-        <v>1223.5</v>
+        <v>1364.5</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -5667,53 +5650,53 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>7.4342</v>
+        <v>0.2412</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>7.4342</v>
+        <v>0.2412</v>
       </c>
       <c r="N57" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O57" t="n">
         <v>100241.18</v>
-      </c>
-      <c r="O57" t="n">
-        <v>107693.32</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>2</v>
       </c>
       <c r="G58" t="n">
-        <v>2084.6</v>
+        <v>1167</v>
       </c>
       <c r="H58" t="n">
-        <v>2113.7</v>
+        <v>1159.4</v>
       </c>
       <c r="J58" t="n">
-        <v>2059.4</v>
+        <v>1223.5</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5721,16 +5704,16 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0.866</v>
+        <v>7.4342</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>0.866</v>
+        <v>7.4342</v>
       </c>
       <c r="N58" t="n">
-        <v>100000</v>
+        <v>100241.18</v>
       </c>
       <c r="O58" t="n">
-        <v>100865.98</v>
+        <v>107693.32</v>
       </c>
     </row>
     <row r="59">
@@ -5740,51 +5723,51 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59" t="n">
-        <v>1641.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H59" t="n">
-        <v>1621</v>
+        <v>2113.7</v>
       </c>
       <c r="J59" t="n">
-        <v>1621</v>
+        <v>2059.4</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_open</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M59" s="5" t="n">
-        <v>-1</v>
+        <v>0.866</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>0.866</v>
       </c>
       <c r="N59" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O59" t="n">
         <v>100865.98</v>
-      </c>
-      <c r="O59" t="n">
-        <v>99857.32000000001</v>
       </c>
     </row>
     <row r="60">
@@ -5794,7 +5777,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -5803,42 +5786,42 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>1581.5</v>
+        <v>1641.5</v>
       </c>
       <c r="H60" t="n">
-        <v>1547.6</v>
+        <v>1621</v>
       </c>
       <c r="J60" t="n">
-        <v>1632.8</v>
+        <v>1621</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.5133</v>
-      </c>
-      <c r="M60" s="2" t="n">
-        <v>1.5133</v>
+        <v>-1</v>
+      </c>
+      <c r="M60" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N60" t="n">
+        <v>100865.98</v>
+      </c>
+      <c r="O60" t="n">
         <v>99857.32000000001</v>
-      </c>
-      <c r="O60" t="n">
-        <v>101368.43</v>
       </c>
     </row>
     <row r="61">
@@ -5848,7 +5831,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -5857,25 +5840,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>2</v>
       </c>
       <c r="G61" t="n">
-        <v>1559</v>
+        <v>1581.5</v>
       </c>
       <c r="H61" t="n">
-        <v>1539.5</v>
+        <v>1547.6</v>
       </c>
       <c r="J61" t="n">
-        <v>1643.2</v>
+        <v>1632.8</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5883,80 +5866,80 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>4.3179</v>
+        <v>1.5133</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>4.3179</v>
+        <v>1.5133</v>
       </c>
       <c r="N61" t="n">
+        <v>99857.32000000001</v>
+      </c>
+      <c r="O61" t="n">
         <v>101368.43</v>
-      </c>
-      <c r="O61" t="n">
-        <v>105745.47</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62" t="n">
-        <v>27907</v>
+        <v>1559</v>
       </c>
       <c r="H62" t="n">
-        <v>27965.76</v>
+        <v>1539.5</v>
       </c>
       <c r="J62" t="n">
-        <v>27965.76</v>
+        <v>1643.2</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_open</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v>-1</v>
+        <v>4.3179</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>4.3179</v>
       </c>
       <c r="N62" t="n">
-        <v>100000</v>
+        <v>101368.43</v>
       </c>
       <c r="O62" t="n">
-        <v>99000</v>
+        <v>105745.47</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -5965,48 +5948,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>2</v>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="G63" t="n">
-        <v>7206.55</v>
+        <v>1769.6</v>
       </c>
       <c r="H63" t="n">
-        <v>7223.26</v>
-      </c>
-      <c r="J63" t="n">
-        <v>7150</v>
+        <v>1798.4</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>exit_open</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
-        <v>3.3842</v>
-      </c>
-      <c r="M63" s="2" t="n">
-        <v>3.3842</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N63" t="n">
-        <v>100000</v>
+        <v>105745.47</v>
       </c>
       <c r="O63" t="n">
-        <v>103384.2</v>
+        <v>105745.47</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -6019,48 +5985,48 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>6957.43</v>
+        <v>27907</v>
       </c>
       <c r="H64" t="n">
-        <v>6965.7</v>
+        <v>27965.76</v>
       </c>
       <c r="J64" t="n">
-        <v>6927.83</v>
+        <v>27965.76</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.5792</v>
-      </c>
-      <c r="M64" s="2" t="n">
-        <v>3.5792</v>
+        <v>-1</v>
+      </c>
+      <c r="M64" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N64" t="n">
         <v>100000</v>
       </c>
       <c r="O64" t="n">
-        <v>103579.2</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -6073,52 +6039,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>1</v>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="G65" t="n">
-        <v>6982.4</v>
+        <v>29892.8</v>
       </c>
       <c r="H65" t="n">
-        <v>6988.83</v>
-      </c>
-      <c r="J65" t="n">
-        <v>7002</v>
+        <v>30074.01</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>-3.0482</v>
-      </c>
-      <c r="M65" s="5" t="n">
-        <v>-3.0482</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N65" t="n">
-        <v>103579.2</v>
+        <v>99000</v>
       </c>
       <c r="O65" t="n">
-        <v>100421.89</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -6127,25 +6076,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>2</v>
       </c>
       <c r="G66" t="n">
-        <v>6982.4</v>
+        <v>7206.55</v>
       </c>
       <c r="H66" t="n">
-        <v>6992.85</v>
+        <v>7223.26</v>
       </c>
       <c r="J66" t="n">
-        <v>6916.64</v>
+        <v>7150</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -6153,26 +6102,26 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>6.2928</v>
+        <v>3.3842</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>6.2928</v>
+        <v>3.3842</v>
       </c>
       <c r="N66" t="n">
-        <v>100421.89</v>
+        <v>100000</v>
       </c>
       <c r="O66" t="n">
-        <v>106741.26</v>
+        <v>103384.2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -6181,42 +6130,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>1</v>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="G67" t="n">
-        <v>6982.4</v>
+        <v>7773</v>
       </c>
       <c r="H67" t="n">
-        <v>6986.84</v>
-      </c>
-      <c r="J67" t="n">
-        <v>6986.84</v>
+        <v>7820.26</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M67" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N67" t="n">
-        <v>106741.26</v>
+        <v>103384.2</v>
       </c>
       <c r="O67" t="n">
-        <v>105673.85</v>
+        <v>103384.2</v>
       </c>
     </row>
     <row r="68">
@@ -6226,61 +6158,61 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G68" t="n">
-        <v>6794.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H68" t="n">
-        <v>6770.77</v>
+        <v>6965.7</v>
       </c>
       <c r="J68" t="n">
-        <v>6769.03</v>
+        <v>6927.83</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_open</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-1.0736</v>
-      </c>
-      <c r="M68" s="5" t="n">
-        <v>-1.0736</v>
+        <v>3.5792</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>3.5792</v>
       </c>
       <c r="N68" t="n">
-        <v>105673.85</v>
+        <v>100000</v>
       </c>
       <c r="O68" t="n">
-        <v>104539.3</v>
+        <v>103579.2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -6289,25 +6221,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>86.081</v>
+        <v>6982.4</v>
       </c>
       <c r="H69" t="n">
-        <v>88.001</v>
+        <v>6988.83</v>
       </c>
       <c r="J69" t="n">
-        <v>88.001</v>
+        <v>7002</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -6315,53 +6247,53 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="N69" t="n">
-        <v>100000</v>
+        <v>103579.2</v>
       </c>
       <c r="O69" t="n">
-        <v>99000</v>
+        <v>100421.89</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>2</v>
       </c>
       <c r="G70" t="n">
-        <v>73.84399999999999</v>
+        <v>6982.4</v>
       </c>
       <c r="H70" t="n">
-        <v>71.999</v>
+        <v>6992.85</v>
       </c>
       <c r="J70" t="n">
-        <v>75.155</v>
+        <v>6916.64</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6369,26 +6301,26 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.7106</v>
+        <v>6.2928</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>0.7106</v>
+        <v>6.2928</v>
       </c>
       <c r="N70" t="n">
-        <v>99000</v>
+        <v>100421.89</v>
       </c>
       <c r="O70" t="n">
-        <v>99703.46000000001</v>
+        <v>106741.26</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -6397,79 +6329,79 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>15</v>
+        <v>6982.4</v>
       </c>
       <c r="H71" t="n">
-        <v>15.26</v>
+        <v>6986.84</v>
       </c>
       <c r="J71" t="n">
-        <v>15.17</v>
+        <v>6986.84</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-0.6538</v>
+        <v>-1</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>-0.6538</v>
+        <v>-1</v>
       </c>
       <c r="N71" t="n">
-        <v>100000</v>
+        <v>106741.26</v>
       </c>
       <c r="O71" t="n">
-        <v>99346.14999999999</v>
+        <v>105673.85</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>20.89</v>
+        <v>6794.4</v>
       </c>
       <c r="H72" t="n">
-        <v>21.07</v>
+        <v>6770.77</v>
       </c>
       <c r="J72" t="n">
-        <v>21.08</v>
+        <v>6769.03</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6477,22 +6409,22 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-1.0556</v>
+        <v>-1.0736</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>-1.0556</v>
+        <v>-1.0736</v>
       </c>
       <c r="N72" t="n">
-        <v>100000</v>
+        <v>105673.85</v>
       </c>
       <c r="O72" t="n">
-        <v>98944.44</v>
+        <v>104539.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -6505,25 +6437,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0.8614000000000001</v>
+        <v>86.081</v>
       </c>
       <c r="H73" t="n">
-        <v>0.8637</v>
+        <v>88.001</v>
       </c>
       <c r="J73" t="n">
-        <v>0.8637</v>
+        <v>88.001</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6546,7 +6478,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -6554,107 +6486,107 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74" t="n">
-        <v>0.8614000000000001</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H74" t="n">
-        <v>0.8658</v>
+        <v>71.999</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8658</v>
+        <v>75.155</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_open</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M74" s="5" t="n">
-        <v>-1</v>
+        <v>0.7106</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>0.7106</v>
       </c>
       <c r="N74" t="n">
         <v>99000</v>
       </c>
       <c r="O74" t="n">
-        <v>98010</v>
+        <v>99703.46000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G75" t="n">
-        <v>0.8467</v>
+        <v>15</v>
       </c>
       <c r="H75" t="n">
-        <v>0.8436</v>
+        <v>15.26</v>
       </c>
       <c r="J75" t="n">
-        <v>0.8498</v>
+        <v>15.17</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>exit_open</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
-      </c>
-      <c r="M75" s="2" t="n">
-        <v>1</v>
+        <v>-0.6538</v>
+      </c>
+      <c r="M75" s="5" t="n">
+        <v>-0.6538</v>
       </c>
       <c r="N75" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O75" t="n">
-        <v>98990.10000000001</v>
+        <v>99346.14999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -6667,25 +6599,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>116.5</v>
+        <v>20.89</v>
       </c>
       <c r="H76" t="n">
-        <v>116.79</v>
+        <v>21.07</v>
       </c>
       <c r="J76" t="n">
-        <v>116.79</v>
+        <v>21.08</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6693,26 +6625,26 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="N76" t="n">
         <v>100000</v>
       </c>
       <c r="O76" t="n">
-        <v>99000</v>
+        <v>98944.44</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -6721,106 +6653,106 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>118.02</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>118.16</v>
+        <v>0.8637</v>
       </c>
       <c r="J77" t="n">
-        <v>118.06</v>
+        <v>0.8637</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-0.2857</v>
+        <v>-1</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>-0.2857</v>
+        <v>-1</v>
       </c>
       <c r="N77" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O77" t="n">
         <v>99000</v>
-      </c>
-      <c r="O77" t="n">
-        <v>98717.14</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>97.81399999999999</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H78" t="n">
-        <v>97.569</v>
+        <v>0.8658</v>
       </c>
       <c r="J78" t="n">
-        <v>98.34999999999999</v>
+        <v>0.8658</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.1878</v>
-      </c>
-      <c r="M78" s="2" t="n">
-        <v>2.1878</v>
+        <v>-1</v>
+      </c>
+      <c r="M78" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N78" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O78" t="n">
-        <v>102187.76</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -6829,52 +6761,52 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>97.714</v>
+        <v>0.8467</v>
       </c>
       <c r="H79" t="n">
-        <v>97.46899999999999</v>
+        <v>0.8436</v>
       </c>
       <c r="J79" t="n">
-        <v>98.11499999999999</v>
+        <v>0.8498</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>data_end</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.6367</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1.6367</v>
+        <v>1</v>
       </c>
       <c r="N79" t="n">
-        <v>102187.76</v>
+        <v>98010</v>
       </c>
       <c r="O79" t="n">
-        <v>103860.3</v>
+        <v>98990.10000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -6883,52 +6815,52 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>99.376</v>
+        <v>116.5</v>
       </c>
       <c r="H80" t="n">
-        <v>99.571</v>
+        <v>116.79</v>
       </c>
       <c r="J80" t="n">
-        <v>99.16500000000001</v>
+        <v>116.79</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.0821</v>
-      </c>
-      <c r="M80" s="2" t="n">
-        <v>1.0821</v>
+        <v>-1</v>
+      </c>
+      <c r="M80" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N80" t="n">
-        <v>103860.3</v>
+        <v>100000</v>
       </c>
       <c r="O80" t="n">
-        <v>104984.12</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -6937,25 +6869,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>2</v>
       </c>
       <c r="G81" t="n">
-        <v>99.246</v>
+        <v>118.02</v>
       </c>
       <c r="H81" t="n">
-        <v>99.501</v>
+        <v>118.16</v>
       </c>
       <c r="J81" t="n">
-        <v>99.145</v>
+        <v>118.06</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6963,16 +6895,16 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.3961</v>
-      </c>
-      <c r="M81" s="2" t="n">
-        <v>0.3961</v>
+        <v>-0.2857</v>
+      </c>
+      <c r="M81" s="5" t="n">
+        <v>-0.2857</v>
       </c>
       <c r="N81" t="n">
-        <v>104984.12</v>
+        <v>99000</v>
       </c>
       <c r="O81" t="n">
-        <v>105399.94</v>
+        <v>98717.14</v>
       </c>
     </row>
     <row r="82">
@@ -6982,34 +6914,34 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>2</v>
       </c>
       <c r="G82" t="n">
-        <v>100.066</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>100.201</v>
+        <v>97.569</v>
       </c>
       <c r="J82" t="n">
-        <v>100</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -7017,16 +6949,16 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.4889</v>
+        <v>2.1878</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>0.4889</v>
+        <v>2.1878</v>
       </c>
       <c r="N82" t="n">
-        <v>105399.94</v>
+        <v>100000</v>
       </c>
       <c r="O82" t="n">
-        <v>105915.23</v>
+        <v>102187.76</v>
       </c>
     </row>
     <row r="83">
@@ -7036,34 +6968,34 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>2</v>
       </c>
       <c r="G83" t="n">
-        <v>100.066</v>
+        <v>97.714</v>
       </c>
       <c r="H83" t="n">
-        <v>100.316</v>
+        <v>97.46899999999999</v>
       </c>
       <c r="J83" t="n">
-        <v>99.34</v>
+        <v>98.11499999999999</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7071,16 +7003,16 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.904</v>
+        <v>1.6367</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2.904</v>
+        <v>1.6367</v>
       </c>
       <c r="N83" t="n">
-        <v>105915.23</v>
+        <v>102187.76</v>
       </c>
       <c r="O83" t="n">
-        <v>108991.01</v>
+        <v>103860.3</v>
       </c>
     </row>
     <row r="84">
@@ -7090,7 +7022,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -7099,42 +7031,42 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G84" t="n">
-        <v>100.066</v>
+        <v>99.376</v>
       </c>
       <c r="H84" t="n">
-        <v>100.361</v>
+        <v>99.571</v>
       </c>
       <c r="J84" t="n">
-        <v>100.361</v>
+        <v>99.16500000000001</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_open</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M84" s="5" t="n">
-        <v>-1</v>
+        <v>1.0821</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>1.0821</v>
       </c>
       <c r="N84" t="n">
-        <v>108991.01</v>
+        <v>103860.3</v>
       </c>
       <c r="O84" t="n">
-        <v>107901.1</v>
+        <v>104984.12</v>
       </c>
     </row>
     <row r="85">
@@ -7144,7 +7076,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -7153,25 +7085,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>2</v>
       </c>
       <c r="G85" t="n">
-        <v>100.621</v>
+        <v>99.246</v>
       </c>
       <c r="H85" t="n">
-        <v>100.911</v>
+        <v>99.501</v>
       </c>
       <c r="J85" t="n">
-        <v>100.805</v>
+        <v>99.145</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7179,16 +7111,16 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>-0.6345</v>
-      </c>
-      <c r="M85" s="5" t="n">
-        <v>-0.6345</v>
+        <v>0.3961</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>0.3961</v>
       </c>
       <c r="N85" t="n">
-        <v>107901.1</v>
+        <v>104984.12</v>
       </c>
       <c r="O85" t="n">
-        <v>107216.48</v>
+        <v>105399.94</v>
       </c>
     </row>
     <row r="86">
@@ -7198,7 +7130,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -7207,25 +7139,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>2</v>
       </c>
       <c r="G86" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H86" t="n">
-        <v>101.526</v>
+        <v>100.201</v>
       </c>
       <c r="J86" t="n">
-        <v>101.15</v>
+        <v>100</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7233,16 +7165,16 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.2696</v>
+        <v>0.4889</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2.2696</v>
+        <v>0.4889</v>
       </c>
       <c r="N86" t="n">
-        <v>107216.48</v>
+        <v>105399.94</v>
       </c>
       <c r="O86" t="n">
-        <v>109649.83</v>
+        <v>105915.23</v>
       </c>
     </row>
     <row r="87">
@@ -7252,7 +7184,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -7261,25 +7193,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F87" t="n">
         <v>2</v>
       </c>
       <c r="G87" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H87" t="n">
-        <v>101.491</v>
+        <v>100.316</v>
       </c>
       <c r="J87" t="n">
-        <v>100.67</v>
+        <v>99.34</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7287,26 +7219,26 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>9.262499999999999</v>
+        <v>2.904</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>9.262499999999999</v>
+        <v>2.904</v>
       </c>
       <c r="N87" t="n">
-        <v>109649.83</v>
+        <v>105915.23</v>
       </c>
       <c r="O87" t="n">
-        <v>119806.14</v>
+        <v>108991.01</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -7315,95 +7247,311 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>121.72</v>
+        <v>100.066</v>
       </c>
       <c r="H88" t="n">
-        <v>123.03</v>
+        <v>100.361</v>
       </c>
       <c r="J88" t="n">
-        <v>115.22</v>
+        <v>100.361</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>4.9618</v>
-      </c>
-      <c r="M88" s="2" t="n">
-        <v>4.9618</v>
+        <v>-1</v>
+      </c>
+      <c r="M88" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N88" t="n">
-        <v>100000</v>
+        <v>108991.01</v>
       </c>
       <c r="O88" t="n">
-        <v>104961.83</v>
+        <v>107901.1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>8</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" t="n">
+        <v>100.621</v>
+      </c>
+      <c r="H89" t="n">
+        <v>100.911</v>
+      </c>
+      <c r="J89" t="n">
+        <v>100.805</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>-0.6345</v>
+      </c>
+      <c r="M89" s="5" t="n">
+        <v>-0.6345</v>
+      </c>
+      <c r="N89" t="n">
+        <v>107901.1</v>
+      </c>
+      <c r="O89" t="n">
+        <v>107216.48</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>9</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H90" t="n">
+        <v>101.526</v>
+      </c>
+      <c r="J90" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>2.2696</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>2.2696</v>
+      </c>
+      <c r="N90" t="n">
+        <v>107216.48</v>
+      </c>
+      <c r="O90" t="n">
+        <v>109649.83</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>10</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>2</v>
+      </c>
+      <c r="G91" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H91" t="n">
+        <v>101.491</v>
+      </c>
+      <c r="J91" t="n">
+        <v>100.67</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>9.262499999999999</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>9.262499999999999</v>
+      </c>
+      <c r="N91" t="n">
+        <v>109649.83</v>
+      </c>
+      <c r="O91" t="n">
+        <v>119806.14</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
           <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
-      <c r="B89" t="n">
-        <v>2</v>
-      </c>
-      <c r="C89" t="inlineStr">
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>2</v>
+      </c>
+      <c r="G92" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H92" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="J92" t="n">
+        <v>115.22</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>4.9618</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>4.9618</v>
+      </c>
+      <c r="N92" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O92" t="n">
+        <v>104961.83</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>2</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="F89" t="n">
-        <v>2</v>
-      </c>
-      <c r="G89" t="n">
+      <c r="F93" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" t="n">
         <v>130.16</v>
       </c>
-      <c r="H89" t="n">
+      <c r="H93" t="n">
         <v>130.94</v>
       </c>
-      <c r="J89" t="n">
+      <c r="J93" t="n">
         <v>139.27</v>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>exit_open</t>
         </is>
       </c>
-      <c r="L89" t="n">
+      <c r="L93" t="n">
         <v>-11.6795</v>
       </c>
-      <c r="M89" s="5" t="n">
+      <c r="M93" s="5" t="n">
         <v>-11.6795</v>
       </c>
-      <c r="N89" t="n">
+      <c r="N93" t="n">
         <v>104961.83</v>
       </c>
-      <c r="O89" t="n">
+      <c r="O93" t="n">
         <v>92702.83</v>
       </c>
     </row>

--- a/output/quickfixopen2_all_markets_daily.xlsx
+++ b/output/quickfixopen2_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
@@ -698,20 +698,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
         <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -720,16 +720,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>17.89</v>
+        <v>16.71</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>117885.42</v>
+        <v>116706.56</v>
       </c>
     </row>
     <row r="6">
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>100</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -986,18 +986,18 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
         <v>4</v>
       </c>
-      <c r="G11" t="n">
-        <v>3</v>
-      </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
@@ -1008,16 +1008,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5.75</v>
+        <v>6.73</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>105745.47</v>
+        <v>106733.16</v>
       </c>
     </row>
     <row r="12">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1056,16 +1056,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>100</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3.38</v>
+        <v>4.22</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>103384.2</v>
+        <v>104215.47</v>
       </c>
     </row>
     <row r="13">
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -1104,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>50</v>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1167,7 +1167,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1203,19 +1203,19 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0.82</v>
+        <v>1.07</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>100824.32</v>
+        <v>101068.12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CME_SOFR_Futures_3M</t>
+          <t>Japanese_Yen_Futures</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1226,17 +1226,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>74</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1250,17 +1250,20 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="4" t="n">
-        <v>0</v>
+      <c r="L16" t="n">
+        <v>100</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>0.82</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>100000</v>
+        <v>100824.32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Global_X_Uranium_ETF</t>
+          <t>CME_SOFR_Futures_3M</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1271,11 +1274,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1305,7 +1308,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Japanese_10_Year_Bond_Futures</t>
+          <t>Global_X_Uranium_ETF</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1316,11 +1319,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1350,7 +1353,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NY_Crude_Oil_Futures</t>
+          <t>Japanese_10_Year_Bond_Futures</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1361,7 +1364,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1395,22 +1398,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Proshares_VIX_Short_Term_Futures_ETF</t>
+          <t>NY_Crude_Oil_Futures</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>145</v>
+        <v>74</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1440,22 +1443,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>US_10_Year_T_Note_Futures</t>
+          <t>Proshares_VIX_Short_Term_Futures_ETF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1485,7 +1488,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EURO_Futures</t>
+          <t>US_10_Year_T_Note_Futures</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1496,20 +1499,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1520,35 +1523,32 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
-        <v>50</v>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v>-0.3</v>
+      <c r="M22" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>99699.46000000001</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>EURO_Futures</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
@@ -1575,37 +1575,37 @@
         <v>-0.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>99703.46000000001</v>
+        <v>99699.46000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>73</v>
+        <v>154</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1617,19 +1617,19 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>-0.65</v>
+        <v>-0.3</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>99346.14999999999</v>
+        <v>99703.46000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1662,16 +1662,16 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>-1</v>
+        <v>-0.65</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>99000</v>
+        <v>99346.14999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixopen2 daily (exit = the open of price bar 2), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-06); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-07 13:34 UTC.</t>
+          <t>quickfixopen2 daily (exit = the open of price bar 2), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-07); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-08 17:31 UTC.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O93"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4942,22 +4942,39 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
       <c r="G44" t="n">
         <v>4305.3</v>
       </c>
       <c r="H44" t="n">
         <v>4363.8</v>
       </c>
+      <c r="J44" t="n">
+        <v>4363.8</v>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N44" t="n">
         <v>117885.42</v>
       </c>
       <c r="O44" t="n">
-        <v>117885.42</v>
+        <v>116706.56</v>
       </c>
     </row>
     <row r="45">
@@ -5449,11 +5466,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -5462,42 +5479,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>1</v>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G54" t="n">
-        <v>3.305</v>
+        <v>6.7286</v>
       </c>
       <c r="H54" t="n">
-        <v>3.354</v>
-      </c>
-      <c r="J54" t="n">
-        <v>3.354</v>
+        <v>6.7656</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N54" t="n">
-        <v>100000</v>
+        <v>102709.36</v>
       </c>
       <c r="O54" t="n">
-        <v>99000</v>
+        <v>102709.36</v>
       </c>
     </row>
     <row r="55">
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -5516,42 +5516,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
         <v>3.305</v>
       </c>
       <c r="H55" t="n">
-        <v>3.356</v>
+        <v>3.354</v>
       </c>
       <c r="J55" t="n">
-        <v>3.016</v>
+        <v>3.354</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>5.6667</v>
-      </c>
-      <c r="M55" s="2" t="n">
-        <v>5.6667</v>
+        <v>-1</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N55" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O55" t="n">
         <v>99000</v>
-      </c>
-      <c r="O55" t="n">
-        <v>104610</v>
       </c>
     </row>
     <row r="56">
@@ -5561,34 +5561,34 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69</v>
+        <v>3.305</v>
       </c>
       <c r="H56" t="n">
-        <v>2.665</v>
+        <v>3.356</v>
       </c>
       <c r="J56" t="n">
-        <v>2.746</v>
+        <v>3.016</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -5596,26 +5596,26 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.24</v>
+        <v>5.6667</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2.24</v>
+        <v>5.6667</v>
       </c>
       <c r="N56" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O56" t="n">
         <v>104610</v>
-      </c>
-      <c r="O56" t="n">
-        <v>106953.26</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -5624,25 +5624,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>2</v>
       </c>
       <c r="G57" t="n">
-        <v>1360.4</v>
+        <v>2.69</v>
       </c>
       <c r="H57" t="n">
-        <v>1343.4</v>
+        <v>2.665</v>
       </c>
       <c r="J57" t="n">
-        <v>1364.5</v>
+        <v>2.746</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -5650,16 +5650,16 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0.2412</v>
+        <v>2.24</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.2412</v>
+        <v>2.24</v>
       </c>
       <c r="N57" t="n">
-        <v>100000</v>
+        <v>104610</v>
       </c>
       <c r="O57" t="n">
-        <v>100241.18</v>
+        <v>106953.26</v>
       </c>
     </row>
     <row r="58">
@@ -5669,7 +5669,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -5678,25 +5678,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>2</v>
       </c>
       <c r="G58" t="n">
-        <v>1167</v>
+        <v>1360.4</v>
       </c>
       <c r="H58" t="n">
-        <v>1159.4</v>
+        <v>1343.4</v>
       </c>
       <c r="J58" t="n">
-        <v>1223.5</v>
+        <v>1364.5</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5704,53 +5704,53 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>7.4342</v>
+        <v>0.2412</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>7.4342</v>
+        <v>0.2412</v>
       </c>
       <c r="N58" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O58" t="n">
         <v>100241.18</v>
-      </c>
-      <c r="O58" t="n">
-        <v>107693.32</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>2</v>
       </c>
       <c r="G59" t="n">
-        <v>2084.6</v>
+        <v>1167</v>
       </c>
       <c r="H59" t="n">
-        <v>2113.7</v>
+        <v>1159.4</v>
       </c>
       <c r="J59" t="n">
-        <v>2059.4</v>
+        <v>1223.5</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5758,70 +5758,53 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.866</v>
+        <v>7.4342</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0.866</v>
+        <v>7.4342</v>
       </c>
       <c r="N59" t="n">
-        <v>100000</v>
+        <v>100241.18</v>
       </c>
       <c r="O59" t="n">
-        <v>100865.98</v>
+        <v>107693.32</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>1</v>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G60" t="n">
-        <v>1641.5</v>
+        <v>1386.6</v>
       </c>
       <c r="H60" t="n">
-        <v>1621</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1621</v>
+        <v>1412.1</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N60" t="n">
-        <v>100865.98</v>
+        <v>107693.32</v>
       </c>
       <c r="O60" t="n">
-        <v>99857.32000000001</v>
+        <v>107693.32</v>
       </c>
     </row>
     <row r="61">
@@ -5831,34 +5814,34 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>2</v>
       </c>
       <c r="G61" t="n">
-        <v>1581.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H61" t="n">
-        <v>1547.6</v>
+        <v>2113.7</v>
       </c>
       <c r="J61" t="n">
-        <v>1632.8</v>
+        <v>2059.4</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5866,16 +5849,16 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.5133</v>
+        <v>0.866</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1.5133</v>
+        <v>0.866</v>
       </c>
       <c r="N61" t="n">
-        <v>99857.32000000001</v>
+        <v>100000</v>
       </c>
       <c r="O61" t="n">
-        <v>101368.43</v>
+        <v>100865.98</v>
       </c>
     </row>
     <row r="62">
@@ -5885,7 +5868,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -5894,42 +5877,42 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>1559</v>
+        <v>1641.5</v>
       </c>
       <c r="H62" t="n">
-        <v>1539.5</v>
+        <v>1621</v>
       </c>
       <c r="J62" t="n">
-        <v>1643.2</v>
+        <v>1621</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>4.3179</v>
-      </c>
-      <c r="M62" s="2" t="n">
-        <v>4.3179</v>
+        <v>-1</v>
+      </c>
+      <c r="M62" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N62" t="n">
-        <v>101368.43</v>
+        <v>100865.98</v>
       </c>
       <c r="O62" t="n">
-        <v>105745.47</v>
+        <v>99857.32000000001</v>
       </c>
     </row>
     <row r="63">
@@ -5939,98 +5922,115 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>2</v>
       </c>
       <c r="G63" t="n">
-        <v>1769.6</v>
+        <v>1581.5</v>
       </c>
       <c r="H63" t="n">
-        <v>1798.4</v>
+        <v>1547.6</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1632.8</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>1.5133</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>1.5133</v>
       </c>
       <c r="N63" t="n">
-        <v>105745.47</v>
+        <v>99857.32000000001</v>
       </c>
       <c r="O63" t="n">
-        <v>105745.47</v>
+        <v>101368.43</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64" t="n">
-        <v>27907</v>
+        <v>1559</v>
       </c>
       <c r="H64" t="n">
-        <v>27965.76</v>
+        <v>1539.5</v>
       </c>
       <c r="J64" t="n">
-        <v>27965.76</v>
+        <v>1643.2</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_open</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v>-1</v>
+        <v>4.3179</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>4.3179</v>
       </c>
       <c r="N64" t="n">
-        <v>100000</v>
+        <v>101368.43</v>
       </c>
       <c r="O64" t="n">
-        <v>99000</v>
+        <v>105745.47</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -6042,28 +6042,45 @@
           <t>2026-08-05</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>2</v>
+      </c>
       <c r="G65" t="n">
-        <v>29892.8</v>
+        <v>1769.6</v>
       </c>
       <c r="H65" t="n">
-        <v>30074.01</v>
+        <v>1798.4</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1742.7</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>0.9340000000000001</v>
       </c>
       <c r="N65" t="n">
-        <v>99000</v>
+        <v>105745.47</v>
       </c>
       <c r="O65" t="n">
-        <v>99000</v>
+        <v>106733.16</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -6076,48 +6093,48 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>7206.55</v>
+        <v>27907</v>
       </c>
       <c r="H66" t="n">
-        <v>7223.26</v>
+        <v>27965.76</v>
       </c>
       <c r="J66" t="n">
-        <v>7150</v>
+        <v>27965.76</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.3842</v>
-      </c>
-      <c r="M66" s="2" t="n">
-        <v>3.3842</v>
+        <v>-1</v>
+      </c>
+      <c r="M66" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N66" t="n">
         <v>100000</v>
       </c>
       <c r="O66" t="n">
-        <v>103384.2</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -6133,28 +6150,45 @@
           <t>2026-08-05</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>2</v>
+      </c>
       <c r="G67" t="n">
-        <v>7773</v>
+        <v>29892.8</v>
       </c>
       <c r="H67" t="n">
-        <v>7820.26</v>
+        <v>30074.01</v>
+      </c>
+      <c r="J67" t="n">
+        <v>29514.25</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>2.089</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>2.089</v>
       </c>
       <c r="N67" t="n">
-        <v>103384.2</v>
+        <v>99000</v>
       </c>
       <c r="O67" t="n">
-        <v>103384.2</v>
+        <v>101068.12</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -6167,25 +6201,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>2</v>
       </c>
       <c r="G68" t="n">
-        <v>6957.43</v>
+        <v>7206.55</v>
       </c>
       <c r="H68" t="n">
-        <v>6965.7</v>
+        <v>7223.26</v>
       </c>
       <c r="J68" t="n">
-        <v>6927.83</v>
+        <v>7150</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -6193,22 +6227,22 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.5792</v>
+        <v>3.3842</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3.5792</v>
+        <v>3.3842</v>
       </c>
       <c r="N68" t="n">
         <v>100000</v>
       </c>
       <c r="O68" t="n">
-        <v>103579.2</v>
+        <v>103384.2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -6221,42 +6255,42 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" t="n">
-        <v>6982.4</v>
+        <v>7773</v>
       </c>
       <c r="H69" t="n">
-        <v>6988.83</v>
+        <v>7820.26</v>
       </c>
       <c r="J69" t="n">
-        <v>7002</v>
+        <v>7735</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_open</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-3.0482</v>
-      </c>
-      <c r="M69" s="5" t="n">
-        <v>-3.0482</v>
+        <v>0.8041</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>0.8041</v>
       </c>
       <c r="N69" t="n">
-        <v>103579.2</v>
+        <v>103384.2</v>
       </c>
       <c r="O69" t="n">
-        <v>100421.89</v>
+        <v>104215.47</v>
       </c>
     </row>
     <row r="70">
@@ -6266,7 +6300,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -6275,25 +6309,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>2</v>
       </c>
       <c r="G70" t="n">
-        <v>6982.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H70" t="n">
-        <v>6992.85</v>
+        <v>6965.7</v>
       </c>
       <c r="J70" t="n">
-        <v>6916.64</v>
+        <v>6927.83</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6301,16 +6335,16 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>6.2928</v>
+        <v>3.5792</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>6.2928</v>
+        <v>3.5792</v>
       </c>
       <c r="N70" t="n">
-        <v>100421.89</v>
+        <v>100000</v>
       </c>
       <c r="O70" t="n">
-        <v>106741.26</v>
+        <v>103579.2</v>
       </c>
     </row>
     <row r="71">
@@ -6320,7 +6354,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -6329,12 +6363,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -6344,10 +6378,10 @@
         <v>6982.4</v>
       </c>
       <c r="H71" t="n">
-        <v>6986.84</v>
+        <v>6988.83</v>
       </c>
       <c r="J71" t="n">
-        <v>6986.84</v>
+        <v>7002</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6355,16 +6389,16 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="N71" t="n">
-        <v>106741.26</v>
+        <v>103579.2</v>
       </c>
       <c r="O71" t="n">
-        <v>105673.85</v>
+        <v>100421.89</v>
       </c>
     </row>
     <row r="72">
@@ -6374,61 +6408,61 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G72" t="n">
-        <v>6794.4</v>
+        <v>6982.4</v>
       </c>
       <c r="H72" t="n">
-        <v>6770.77</v>
+        <v>6992.85</v>
       </c>
       <c r="J72" t="n">
-        <v>6769.03</v>
+        <v>6916.64</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_open</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-1.0736</v>
-      </c>
-      <c r="M72" s="5" t="n">
-        <v>-1.0736</v>
+        <v>6.2928</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>6.2928</v>
       </c>
       <c r="N72" t="n">
-        <v>105673.85</v>
+        <v>100421.89</v>
       </c>
       <c r="O72" t="n">
-        <v>104539.3</v>
+        <v>106741.26</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -6437,25 +6471,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>86.081</v>
+        <v>6982.4</v>
       </c>
       <c r="H73" t="n">
-        <v>88.001</v>
+        <v>6986.84</v>
       </c>
       <c r="J73" t="n">
-        <v>88.001</v>
+        <v>6986.84</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6469,20 +6503,20 @@
         <v>-1</v>
       </c>
       <c r="N73" t="n">
-        <v>100000</v>
+        <v>106741.26</v>
       </c>
       <c r="O73" t="n">
-        <v>99000</v>
+        <v>105673.85</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -6491,48 +6525,48 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>73.84399999999999</v>
+        <v>6794.4</v>
       </c>
       <c r="H74" t="n">
-        <v>71.999</v>
+        <v>6770.77</v>
       </c>
       <c r="J74" t="n">
-        <v>75.155</v>
+        <v>6769.03</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.7106</v>
-      </c>
-      <c r="M74" s="2" t="n">
-        <v>0.7106</v>
+        <v>-1.0736</v>
+      </c>
+      <c r="M74" s="5" t="n">
+        <v>-1.0736</v>
       </c>
       <c r="N74" t="n">
-        <v>99000</v>
+        <v>105673.85</v>
       </c>
       <c r="O74" t="n">
-        <v>99703.46000000001</v>
+        <v>104539.3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -6545,102 +6579,102 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>15</v>
+        <v>86.081</v>
       </c>
       <c r="H75" t="n">
-        <v>15.26</v>
+        <v>88.001</v>
       </c>
       <c r="J75" t="n">
-        <v>15.17</v>
+        <v>88.001</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-0.6538</v>
+        <v>-1</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>-0.6538</v>
+        <v>-1</v>
       </c>
       <c r="N75" t="n">
         <v>100000</v>
       </c>
       <c r="O75" t="n">
-        <v>99346.14999999999</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76" t="n">
-        <v>20.89</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>21.07</v>
+        <v>71.999</v>
       </c>
       <c r="J76" t="n">
-        <v>21.08</v>
+        <v>75.155</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_open</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-1.0556</v>
-      </c>
-      <c r="M76" s="5" t="n">
-        <v>-1.0556</v>
+        <v>0.7106</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>0.7106</v>
       </c>
       <c r="N76" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O76" t="n">
-        <v>98944.44</v>
+        <v>99703.46000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -6653,52 +6687,52 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G77" t="n">
-        <v>0.8614000000000001</v>
+        <v>15</v>
       </c>
       <c r="H77" t="n">
-        <v>0.8637</v>
+        <v>15.26</v>
       </c>
       <c r="J77" t="n">
-        <v>0.8637</v>
+        <v>15.17</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_open</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-1</v>
+        <v>-0.6538</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>-1</v>
+        <v>-0.6538</v>
       </c>
       <c r="N77" t="n">
         <v>100000</v>
       </c>
       <c r="O77" t="n">
-        <v>99000</v>
+        <v>99346.14999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -6707,25 +6741,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8614000000000001</v>
+        <v>20.89</v>
       </c>
       <c r="H78" t="n">
-        <v>0.8658</v>
+        <v>21.07</v>
       </c>
       <c r="J78" t="n">
-        <v>0.8658</v>
+        <v>21.08</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6733,16 +6767,16 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="N78" t="n">
-        <v>99000</v>
+        <v>100000</v>
       </c>
       <c r="O78" t="n">
-        <v>98010</v>
+        <v>98944.44</v>
       </c>
     </row>
     <row r="79">
@@ -6752,61 +6786,61 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>0.8467</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H79" t="n">
-        <v>0.8436</v>
+        <v>0.8637</v>
       </c>
       <c r="J79" t="n">
-        <v>0.8498</v>
+        <v>0.8637</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1</v>
-      </c>
-      <c r="M79" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
+      </c>
+      <c r="M79" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N79" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O79" t="n">
-        <v>98990.10000000001</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -6815,25 +6849,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>116.5</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>116.79</v>
+        <v>0.8658</v>
       </c>
       <c r="J80" t="n">
-        <v>116.79</v>
+        <v>0.8658</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6847,70 +6881,70 @@
         <v>-1</v>
       </c>
       <c r="N80" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O80" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>118.02</v>
+        <v>0.8467</v>
       </c>
       <c r="H81" t="n">
-        <v>118.16</v>
+        <v>0.8436</v>
       </c>
       <c r="J81" t="n">
-        <v>118.06</v>
+        <v>0.8498</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>data_end</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>-0.2857</v>
-      </c>
-      <c r="M81" s="5" t="n">
-        <v>-0.2857</v>
+        <v>1</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N81" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
       <c r="O81" t="n">
-        <v>98717.14</v>
+        <v>98990.10000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -6918,53 +6952,53 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>97.81399999999999</v>
+        <v>116.5</v>
       </c>
       <c r="H82" t="n">
-        <v>97.569</v>
+        <v>116.79</v>
       </c>
       <c r="J82" t="n">
-        <v>98.34999999999999</v>
+        <v>116.79</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.1878</v>
-      </c>
-      <c r="M82" s="2" t="n">
-        <v>2.1878</v>
+        <v>-1</v>
+      </c>
+      <c r="M82" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N82" t="n">
         <v>100000</v>
       </c>
       <c r="O82" t="n">
-        <v>102187.76</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -6972,30 +7006,30 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>2</v>
       </c>
       <c r="G83" t="n">
-        <v>97.714</v>
+        <v>118.02</v>
       </c>
       <c r="H83" t="n">
-        <v>97.46899999999999</v>
+        <v>118.16</v>
       </c>
       <c r="J83" t="n">
-        <v>98.11499999999999</v>
+        <v>118.06</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7003,16 +7037,16 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.6367</v>
-      </c>
-      <c r="M83" s="2" t="n">
-        <v>1.6367</v>
+        <v>-0.2857</v>
+      </c>
+      <c r="M83" s="5" t="n">
+        <v>-0.2857</v>
       </c>
       <c r="N83" t="n">
-        <v>102187.76</v>
+        <v>99000</v>
       </c>
       <c r="O83" t="n">
-        <v>103860.3</v>
+        <v>98717.14</v>
       </c>
     </row>
     <row r="84">
@@ -7022,34 +7056,34 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>2</v>
       </c>
       <c r="G84" t="n">
-        <v>99.376</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>99.571</v>
+        <v>97.569</v>
       </c>
       <c r="J84" t="n">
-        <v>99.16500000000001</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7057,16 +7091,16 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.0821</v>
+        <v>2.1878</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1.0821</v>
+        <v>2.1878</v>
       </c>
       <c r="N84" t="n">
-        <v>103860.3</v>
+        <v>100000</v>
       </c>
       <c r="O84" t="n">
-        <v>104984.12</v>
+        <v>102187.76</v>
       </c>
     </row>
     <row r="85">
@@ -7076,34 +7110,34 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>2</v>
       </c>
       <c r="G85" t="n">
-        <v>99.246</v>
+        <v>97.714</v>
       </c>
       <c r="H85" t="n">
-        <v>99.501</v>
+        <v>97.46899999999999</v>
       </c>
       <c r="J85" t="n">
-        <v>99.145</v>
+        <v>98.11499999999999</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7111,16 +7145,16 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.3961</v>
+        <v>1.6367</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>0.3961</v>
+        <v>1.6367</v>
       </c>
       <c r="N85" t="n">
-        <v>104984.12</v>
+        <v>102187.76</v>
       </c>
       <c r="O85" t="n">
-        <v>105399.94</v>
+        <v>103860.3</v>
       </c>
     </row>
     <row r="86">
@@ -7130,7 +7164,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -7139,25 +7173,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>2</v>
       </c>
       <c r="G86" t="n">
-        <v>100.066</v>
+        <v>99.376</v>
       </c>
       <c r="H86" t="n">
-        <v>100.201</v>
+        <v>99.571</v>
       </c>
       <c r="J86" t="n">
-        <v>100</v>
+        <v>99.16500000000001</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7165,16 +7199,16 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0.4889</v>
+        <v>1.0821</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>0.4889</v>
+        <v>1.0821</v>
       </c>
       <c r="N86" t="n">
-        <v>105399.94</v>
+        <v>103860.3</v>
       </c>
       <c r="O86" t="n">
-        <v>105915.23</v>
+        <v>104984.12</v>
       </c>
     </row>
     <row r="87">
@@ -7184,7 +7218,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -7193,25 +7227,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F87" t="n">
         <v>2</v>
       </c>
       <c r="G87" t="n">
-        <v>100.066</v>
+        <v>99.246</v>
       </c>
       <c r="H87" t="n">
-        <v>100.316</v>
+        <v>99.501</v>
       </c>
       <c r="J87" t="n">
-        <v>99.34</v>
+        <v>99.145</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7219,16 +7253,16 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.904</v>
+        <v>0.3961</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2.904</v>
+        <v>0.3961</v>
       </c>
       <c r="N87" t="n">
-        <v>105915.23</v>
+        <v>104984.12</v>
       </c>
       <c r="O87" t="n">
-        <v>108991.01</v>
+        <v>105399.94</v>
       </c>
     </row>
     <row r="88">
@@ -7238,7 +7272,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -7247,42 +7281,42 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G88" t="n">
         <v>100.066</v>
       </c>
       <c r="H88" t="n">
-        <v>100.361</v>
+        <v>100.201</v>
       </c>
       <c r="J88" t="n">
-        <v>100.361</v>
+        <v>100</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_open</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M88" s="5" t="n">
-        <v>-1</v>
+        <v>0.4889</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>0.4889</v>
       </c>
       <c r="N88" t="n">
-        <v>108991.01</v>
+        <v>105399.94</v>
       </c>
       <c r="O88" t="n">
-        <v>107901.1</v>
+        <v>105915.23</v>
       </c>
     </row>
     <row r="89">
@@ -7292,7 +7326,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -7301,25 +7335,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>2</v>
       </c>
       <c r="G89" t="n">
-        <v>100.621</v>
+        <v>100.066</v>
       </c>
       <c r="H89" t="n">
-        <v>100.911</v>
+        <v>100.316</v>
       </c>
       <c r="J89" t="n">
-        <v>100.805</v>
+        <v>99.34</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -7327,16 +7361,16 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-0.6345</v>
-      </c>
-      <c r="M89" s="5" t="n">
-        <v>-0.6345</v>
+        <v>2.904</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>2.904</v>
       </c>
       <c r="N89" t="n">
-        <v>107901.1</v>
+        <v>105915.23</v>
       </c>
       <c r="O89" t="n">
-        <v>107216.48</v>
+        <v>108991.01</v>
       </c>
     </row>
     <row r="90">
@@ -7346,7 +7380,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -7355,42 +7389,42 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H90" t="n">
-        <v>101.526</v>
+        <v>100.361</v>
       </c>
       <c r="J90" t="n">
-        <v>101.15</v>
+        <v>100.361</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.2696</v>
-      </c>
-      <c r="M90" s="2" t="n">
-        <v>2.2696</v>
+        <v>-1</v>
+      </c>
+      <c r="M90" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N90" t="n">
-        <v>107216.48</v>
+        <v>108991.01</v>
       </c>
       <c r="O90" t="n">
-        <v>109649.83</v>
+        <v>107901.1</v>
       </c>
     </row>
     <row r="91">
@@ -7400,7 +7434,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -7409,25 +7443,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F91" t="n">
         <v>2</v>
       </c>
       <c r="G91" t="n">
-        <v>101.411</v>
+        <v>100.621</v>
       </c>
       <c r="H91" t="n">
-        <v>101.491</v>
+        <v>100.911</v>
       </c>
       <c r="J91" t="n">
-        <v>100.67</v>
+        <v>100.805</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -7435,26 +7469,26 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>9.262499999999999</v>
-      </c>
-      <c r="M91" s="2" t="n">
-        <v>9.262499999999999</v>
+        <v>-0.6345</v>
+      </c>
+      <c r="M91" s="5" t="n">
+        <v>-0.6345</v>
       </c>
       <c r="N91" t="n">
-        <v>109649.83</v>
+        <v>107901.1</v>
       </c>
       <c r="O91" t="n">
-        <v>119806.14</v>
+        <v>107216.48</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -7463,25 +7497,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F92" t="n">
         <v>2</v>
       </c>
       <c r="G92" t="n">
-        <v>121.72</v>
+        <v>101.411</v>
       </c>
       <c r="H92" t="n">
-        <v>123.03</v>
+        <v>101.526</v>
       </c>
       <c r="J92" t="n">
-        <v>115.22</v>
+        <v>101.15</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -7489,69 +7523,177 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>4.9618</v>
+        <v>2.2696</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>4.9618</v>
+        <v>2.2696</v>
       </c>
       <c r="N92" t="n">
-        <v>100000</v>
+        <v>107216.48</v>
       </c>
       <c r="O92" t="n">
-        <v>104961.83</v>
+        <v>109649.83</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>10</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H93" t="n">
+        <v>101.491</v>
+      </c>
+      <c r="J93" t="n">
+        <v>100.67</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>9.262499999999999</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>9.262499999999999</v>
+      </c>
+      <c r="N93" t="n">
+        <v>109649.83</v>
+      </c>
+      <c r="O93" t="n">
+        <v>119806.14</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
-      <c r="B93" t="n">
-        <v>2</v>
-      </c>
-      <c r="C93" t="inlineStr">
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>2</v>
+      </c>
+      <c r="G94" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H94" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="J94" t="n">
+        <v>115.22</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>4.9618</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>4.9618</v>
+      </c>
+      <c r="N94" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O94" t="n">
+        <v>104961.83</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>2</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="F93" t="n">
-        <v>2</v>
-      </c>
-      <c r="G93" t="n">
+      <c r="F95" t="n">
+        <v>2</v>
+      </c>
+      <c r="G95" t="n">
         <v>130.16</v>
       </c>
-      <c r="H93" t="n">
+      <c r="H95" t="n">
         <v>130.94</v>
       </c>
-      <c r="J93" t="n">
+      <c r="J95" t="n">
         <v>139.27</v>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t>exit_open</t>
         </is>
       </c>
-      <c r="L93" t="n">
+      <c r="L95" t="n">
         <v>-11.6795</v>
       </c>
-      <c r="M93" s="5" t="n">
+      <c r="M95" s="5" t="n">
         <v>-11.6795</v>
       </c>
-      <c r="N93" t="n">
+      <c r="N95" t="n">
         <v>104961.83</v>
       </c>
-      <c r="O93" t="n">
+      <c r="O95" t="n">
         <v>92702.83</v>
       </c>
     </row>
